--- a/Results_experiment/exp_2/summary.xlsx
+++ b/Results_experiment/exp_2/summary.xlsx
@@ -447,13 +447,13 @@
         <v>3055</v>
       </c>
       <c r="D2">
-        <v>0.7205861510496392</v>
+        <v>0.7059903787732098</v>
       </c>
       <c r="E2">
-        <v>3.821724442185262</v>
+        <v>3.920271788782953</v>
       </c>
       <c r="F2">
-        <v>2.74927186608656</v>
+        <v>2.807709525935291</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>3014</v>
       </c>
       <c r="D3">
-        <v>0.7090944921704067</v>
+        <v>0.710719392070887</v>
       </c>
       <c r="E3">
-        <v>5.832081966734782</v>
+        <v>5.815771138234606</v>
       </c>
       <c r="F3">
-        <v>4.142586971903421</v>
+        <v>4.148778035347141</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>2753</v>
       </c>
       <c r="D4">
-        <v>0.6445404868994082</v>
+        <v>0.6623176435872244</v>
       </c>
       <c r="E4">
-        <v>5.765909610081775</v>
+        <v>5.619878726710406</v>
       </c>
       <c r="F4">
-        <v>4.109831502346724</v>
+        <v>4.008737230744423</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>2231</v>
       </c>
       <c r="D5">
-        <v>0.5221235701486786</v>
+        <v>0.5274655064646363</v>
       </c>
       <c r="E5">
-        <v>2.969807288463278</v>
+        <v>2.95316166074286</v>
       </c>
       <c r="F5">
-        <v>2.049185661078166</v>
+        <v>2.066548697033718</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>1838</v>
       </c>
       <c r="D6">
-        <v>0.6170514882853904</v>
+        <v>0.624581392933631</v>
       </c>
       <c r="E6">
-        <v>4.099242915547472</v>
+        <v>4.058741188218487</v>
       </c>
       <c r="F6">
-        <v>2.961198234707927</v>
+        <v>2.968694691809461</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>1534</v>
       </c>
       <c r="D7">
-        <v>0.7668288536386531</v>
+        <v>0.7500243014609987</v>
       </c>
       <c r="E7">
-        <v>3.67715260154035</v>
+        <v>3.807353003359272</v>
       </c>
       <c r="F7">
-        <v>2.731653050510425</v>
+        <v>2.77185941456001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>1348</v>
       </c>
       <c r="D8">
-        <v>0.6465822423180582</v>
+        <v>0.61984661670404</v>
       </c>
       <c r="E8">
-        <v>2.859734003338842</v>
+        <v>2.965929924227797</v>
       </c>
       <c r="F8">
-        <v>2.204424125176889</v>
+        <v>2.288658977465497</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>572</v>
       </c>
       <c r="D9">
-        <v>0.5195605940564696</v>
+        <v>0.4866586722057964</v>
       </c>
       <c r="E9">
-        <v>6.622655537159074</v>
+        <v>6.845670174313258</v>
       </c>
       <c r="F9">
-        <v>4.317846826237181</v>
+        <v>4.381440640532452</v>
       </c>
     </row>
   </sheetData>
